--- a/experiment2.xlsx
+++ b/experiment2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\CTOP\git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760187D9-451E-4C41-B037-87B1C3B11B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD3E6B5-68F6-462F-B6E2-4148C44E9007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-4270" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="97">
   <si>
     <t>Instance</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -323,6 +323,10 @@
   </si>
   <si>
     <t>LDMA5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>time</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -330,7 +334,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -344,6 +348,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -366,15 +377,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -655,25 +669,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="3"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="2"/>
       <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -681,16 +696,22 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -700,17 +721,23 @@
       <c r="C3">
         <v>0.32535020334386888</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="4">
+        <v>-2.5147126990973701</v>
+      </c>
+      <c r="E3">
         <v>0.45045045045045046</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>0.27112516945323095</v>
       </c>
-      <c r="F3">
+      <c r="G3" s="4">
+        <v>7.1923067618377896</v>
+      </c>
+      <c r="H3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -720,17 +747,23 @@
       <c r="C4">
         <v>0.11443661971830585</v>
       </c>
-      <c r="D4">
-        <v>0</v>
+      <c r="D4" s="4">
+        <v>-6.5889487525617998</v>
       </c>
       <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>0.1584507042253481</v>
       </c>
-      <c r="F4">
+      <c r="G4" s="4">
+        <v>-6.4552829199573898</v>
+      </c>
+      <c r="H4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -740,17 +773,23 @@
       <c r="C5">
         <v>0.15255930087391456</v>
       </c>
-      <c r="D5">
-        <v>0</v>
+      <c r="D5" s="4">
+        <v>-5.8204282027163998</v>
       </c>
       <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>9.9875156054935132E-2</v>
       </c>
-      <c r="F5">
+      <c r="G5" s="4">
+        <v>-5.7983267267270904</v>
+      </c>
+      <c r="H5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -760,17 +799,23 @@
       <c r="C6">
         <v>0.29353861686015525</v>
       </c>
-      <c r="D6">
-        <v>0</v>
+      <c r="D6" s="4">
+        <v>-3.9111744047990999</v>
       </c>
       <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>7.5719333669852229E-2</v>
       </c>
-      <c r="F6">
+      <c r="G6" s="4">
+        <v>-2.5507160029486</v>
+      </c>
+      <c r="H6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -780,17 +825,23 @@
       <c r="C7">
         <v>0.24864957558088518</v>
       </c>
-      <c r="D7">
-        <v>0</v>
+      <c r="D7" s="4">
+        <v>-7.7845494126487003</v>
       </c>
       <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>0.25722369887678986</v>
       </c>
-      <c r="F7">
+      <c r="G7" s="4">
+        <v>-5.57786764243777</v>
+      </c>
+      <c r="H7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -800,17 +851,23 @@
       <c r="C8">
         <v>-1.6220600162209692E-2</v>
       </c>
-      <c r="D8">
-        <v>0</v>
+      <c r="D8" s="4">
+        <v>-3.5865683432744002</v>
       </c>
       <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>-3.2441200324419384E-2</v>
       </c>
-      <c r="F8">
+      <c r="G8" s="4">
+        <v>-1.6814612552049999</v>
+      </c>
+      <c r="H8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -820,17 +877,23 @@
       <c r="C9">
         <v>0</v>
       </c>
-      <c r="D9">
-        <v>0</v>
+      <c r="D9" s="4">
+        <v>-2.5942822248720998</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <v>-1.1329420540704001</v>
+      </c>
+      <c r="H9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -840,17 +903,23 @@
       <c r="C10">
         <v>0.3968253968253968</v>
       </c>
-      <c r="D10">
-        <v>0</v>
+      <c r="D10" s="4">
+        <v>-6.3185550154136001</v>
       </c>
       <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>0.14991181657848726</v>
       </c>
-      <c r="F10">
+      <c r="G10" s="4">
+        <v>-4.2853027556014602</v>
+      </c>
+      <c r="H10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -860,17 +929,23 @@
       <c r="C11">
         <v>0.18102824040550325</v>
       </c>
-      <c r="D11">
-        <v>0</v>
+      <c r="D11" s="4">
+        <v>-4.41726768283461</v>
       </c>
       <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>0.13577118030412744</v>
       </c>
-      <c r="F11">
+      <c r="G11" s="4">
+        <v>-1.51918242438401</v>
+      </c>
+      <c r="H11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -880,17 +955,23 @@
       <c r="C12">
         <v>0.20097136158098231</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="4">
+        <v>-3.0424375263273999</v>
+      </c>
+      <c r="E12">
         <v>0.41736227045075125</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>0.18422374811589728</v>
       </c>
-      <c r="F12">
+      <c r="G12" s="4">
+        <v>3.2232432450070099</v>
+      </c>
+      <c r="H12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -900,17 +981,23 @@
       <c r="C13">
         <v>0.37280875703974342</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="4">
+        <v>-2.3946369480378</v>
+      </c>
+      <c r="E13">
         <v>0.23677979479084454</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>0.42833346553502749</v>
       </c>
-      <c r="F13">
+      <c r="G13" s="4">
+        <v>1.25763714981704</v>
+      </c>
+      <c r="H13">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -920,17 +1007,23 @@
       <c r="C14">
         <v>0.15424957581366652</v>
       </c>
-      <c r="D14">
-        <v>0</v>
+      <c r="D14" s="4">
+        <v>-4.5195398026995799E-2</v>
       </c>
       <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
         <v>7.7124787906833261E-2</v>
       </c>
-      <c r="F14">
+      <c r="G14" s="4">
+        <v>15.128485843201</v>
+      </c>
+      <c r="H14">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -940,17 +1033,23 @@
       <c r="C15">
         <v>0.39056849414146277</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="4">
+        <v>-5.8444151788331897</v>
+      </c>
+      <c r="E15">
         <v>0.28880866425992779</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>0.39056849414146277</v>
       </c>
-      <c r="F15">
+      <c r="G15" s="4">
+        <v>-6.5441430017543096</v>
+      </c>
+      <c r="H15">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -960,17 +1059,23 @@
       <c r="C16">
         <v>4.4189129474142663E-2</v>
       </c>
-      <c r="D16">
-        <v>0</v>
+      <c r="D16" s="4">
+        <v>-2.96106813535429</v>
       </c>
       <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
         <v>3.6824274561791132E-2</v>
       </c>
-      <c r="F16">
+      <c r="G16" s="4">
+        <v>2.3570880615336898E-2</v>
+      </c>
+      <c r="H16">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -980,17 +1085,23 @@
       <c r="C17">
         <v>0.29775197260681846</v>
       </c>
-      <c r="D17">
-        <v>0</v>
+      <c r="D17" s="4">
+        <v>-4.9065850531554096</v>
       </c>
       <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
         <v>0.12654458835790125</v>
       </c>
-      <c r="F17">
+      <c r="G17" s="4">
+        <v>-1.2181743796840101</v>
+      </c>
+      <c r="H17">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1000,17 +1111,23 @@
       <c r="C18">
         <v>0.1336898395721989</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="4">
+        <v>-5.6414533779824003</v>
+      </c>
+      <c r="E18">
         <v>7.0323488045007029E-2</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>9.8508302842674561E-2</v>
       </c>
-      <c r="F18">
+      <c r="G18" s="4">
+        <v>-4.9814398576630898</v>
+      </c>
+      <c r="H18">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1020,17 +1137,23 @@
       <c r="C19">
         <v>0.20591824283099797</v>
       </c>
-      <c r="D19">
-        <v>0</v>
+      <c r="D19" s="4">
+        <v>-1.2505774293419101</v>
       </c>
       <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
         <v>0.23642464917633743</v>
       </c>
-      <c r="F19">
+      <c r="G19" s="4">
+        <v>2.68517011573699</v>
+      </c>
+      <c r="H19">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1040,17 +1163,23 @@
       <c r="C20">
         <v>0.26269025728191792</v>
       </c>
-      <c r="D20">
-        <v>0</v>
+      <c r="D20" s="4">
+        <v>-5.5520931061840999</v>
       </c>
       <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
         <v>0.15452368075407555</v>
       </c>
-      <c r="F20">
+      <c r="G20" s="4">
+        <v>-2.2307857925500101</v>
+      </c>
+      <c r="H20">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -1060,17 +1189,23 @@
       <c r="C21">
         <v>0.19002375296912835</v>
       </c>
-      <c r="D21">
-        <v>0</v>
+      <c r="D21" s="4">
+        <v>-4.7873343911037098</v>
       </c>
       <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
         <v>6.3341250989703446E-2</v>
       </c>
-      <c r="F21">
+      <c r="G21" s="4">
+        <v>-4.5813046636549002</v>
+      </c>
+      <c r="H21">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -1080,17 +1215,23 @@
       <c r="C22">
         <v>0.23269342641070717</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="4">
+        <v>-2.96276578249641</v>
+      </c>
+      <c r="E22">
         <v>-7.2568940493468792E-2</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>-1.45433391506723E-2</v>
       </c>
-      <c r="F22">
+      <c r="G22" s="4">
+        <v>10.332366325134499</v>
+      </c>
+      <c r="H22">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -1100,17 +1241,23 @@
       <c r="C23">
         <v>0.50609451849740794</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="4">
+        <v>-1.2880736250553799</v>
+      </c>
+      <c r="E23">
         <v>0.2130681818181818</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>0.66291253831350638</v>
       </c>
-      <c r="F23">
+      <c r="G23" s="4">
+        <v>-9.0065061660749794</v>
+      </c>
+      <c r="H23">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -1120,17 +1267,23 @@
       <c r="C24">
         <v>0.3639110134578537</v>
       </c>
-      <c r="D24">
-        <v>0</v>
+      <c r="D24" s="4">
+        <v>-3.0447164254521102</v>
       </c>
       <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
         <v>0.39824224114255569</v>
       </c>
-      <c r="F24">
+      <c r="G24" s="4">
+        <v>-1.2829695738859901</v>
+      </c>
+      <c r="H24">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -1140,17 +1293,23 @@
       <c r="C25">
         <v>0.3735296008227903</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="4">
+        <v>-6.8757845892974903</v>
+      </c>
+      <c r="E25">
         <v>0.19230769230769232</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>0.23783505817317258</v>
       </c>
-      <c r="F25">
+      <c r="G25" s="4">
+        <v>-4.4078254769107001</v>
+      </c>
+      <c r="H25">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -1160,17 +1319,23 @@
       <c r="C26">
         <v>0.15034645051640441</v>
       </c>
-      <c r="D26">
-        <v>0</v>
+      <c r="D26" s="4">
+        <v>-5.1959632967613896</v>
       </c>
       <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
         <v>7.8441626356389432E-2</v>
       </c>
-      <c r="F26">
+      <c r="G26" s="4">
+        <v>-0.46255563995961602</v>
+      </c>
+      <c r="H26">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -1180,17 +1345,23 @@
       <c r="C27">
         <v>0.66089485162910588</v>
       </c>
-      <c r="D27">
-        <v>0</v>
+      <c r="D27" s="4">
+        <v>-6.4085676107818097</v>
       </c>
       <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
         <v>0.54854272685215477</v>
       </c>
-      <c r="F27">
+      <c r="G27" s="4">
+        <v>-7.1194156955790104</v>
+      </c>
+      <c r="H27">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -1200,17 +1371,23 @@
       <c r="C28">
         <v>0.10599164536442705</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="4">
+        <v>15.625108857533</v>
+      </c>
+      <c r="E28">
         <v>0.18656716417910446</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>9.3522040027433126E-2</v>
       </c>
-      <c r="F28">
+      <c r="G28" s="4">
+        <v>16.406905573559001</v>
+      </c>
+      <c r="H28">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -1220,17 +1397,23 @@
       <c r="C29">
         <v>4.0952835983885674E-2</v>
       </c>
-      <c r="D29">
-        <v>0</v>
+      <c r="D29" s="4">
+        <v>-6.6689500830081903</v>
       </c>
       <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
         <v>-6.825472663981981E-2</v>
       </c>
-      <c r="F29">
+      <c r="G29" s="4">
+        <v>12.399638591704999</v>
+      </c>
+      <c r="H29">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -1240,17 +1423,23 @@
       <c r="C30">
         <v>0.17009488191703934</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="4">
+        <v>-6.7212959088875897</v>
+      </c>
+      <c r="E30">
         <v>6.9108500345542501E-2</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>2.7702749497893961E-2</v>
       </c>
-      <c r="F30">
+      <c r="G30" s="4">
+        <v>-6.5693183747060999</v>
+      </c>
+      <c r="H30">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -1260,17 +1449,23 @@
       <c r="C31">
         <v>0.37366046249296259</v>
       </c>
-      <c r="D31">
-        <v>0</v>
+      <c r="D31" s="4">
+        <v>-4.7148240342312002</v>
       </c>
       <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
         <v>0.25380710659899436</v>
       </c>
-      <c r="F31">
+      <c r="G31" s="4">
+        <v>-5.4472399561714004</v>
+      </c>
+      <c r="H31">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -1280,17 +1475,23 @@
       <c r="C32">
         <v>0.31162267666124033</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="4">
+        <v>-1.9266835736718999</v>
+      </c>
+      <c r="E32">
         <v>0.19292604501607716</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>0.38882069730397939</v>
       </c>
-      <c r="F32">
+      <c r="G32" s="4">
+        <v>17.352908379799999</v>
+      </c>
+      <c r="H32">
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -1300,17 +1501,23 @@
       <c r="C33">
         <v>6.9160641307759133E-2</v>
       </c>
-      <c r="D33">
-        <v>0</v>
+      <c r="D33" s="4">
+        <v>-3.4153833356437899</v>
       </c>
       <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
         <v>3.7723986167866021E-2</v>
       </c>
-      <c r="F33">
+      <c r="G33" s="4">
+        <v>-3.8838021587882898</v>
+      </c>
+      <c r="H33">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -1320,17 +1527,23 @@
       <c r="C34">
         <v>0.15603545125452503</v>
       </c>
-      <c r="D34">
-        <v>0</v>
+      <c r="D34" s="4">
+        <v>-5.4231537449182001</v>
       </c>
       <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
         <v>4.9931344401445164E-2</v>
       </c>
-      <c r="F34">
+      <c r="G34" s="4">
+        <v>-3.9518929192900099</v>
+      </c>
+      <c r="H34">
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -1340,17 +1553,23 @@
       <c r="C35">
         <v>1.2330456226883196E-2</v>
       </c>
-      <c r="D35">
-        <v>0</v>
+      <c r="D35" s="4">
+        <v>-6.9679930256428104</v>
       </c>
       <c r="E35">
         <v>0</v>
       </c>
       <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35" s="4">
+        <v>-5.6319889547518001</v>
+      </c>
+      <c r="H35">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -1360,17 +1579,23 @@
       <c r="C36">
         <v>5.4831241623010292E-2</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="4">
+        <v>-5.5996301660913002</v>
+      </c>
+      <c r="E36">
         <v>6.0864272671941569E-2</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>4.2646521262339795E-2</v>
       </c>
-      <c r="F36">
+      <c r="G36" s="4">
+        <v>-2.45730002558181</v>
+      </c>
+      <c r="H36">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -1380,17 +1605,23 @@
       <c r="C37">
         <v>9.0618014861354429E-2</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="4">
+        <v>-6.6840119275156997</v>
+      </c>
+      <c r="E37">
         <v>6.0350030175015092E-2</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>1.2082401981516673E-2</v>
       </c>
-      <c r="F37">
+      <c r="G37" s="4">
+        <v>-1.6985582862452</v>
+      </c>
+      <c r="H37">
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -1400,17 +1631,23 @@
       <c r="C38">
         <v>5.9315499140006177E-3</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="4">
+        <v>-7.4277116597010897</v>
+      </c>
+      <c r="E38">
         <v>5.9276822762299938E-2</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>1.186309982798775E-2</v>
       </c>
-      <c r="F38">
+      <c r="G38" s="4">
+        <v>-5.9526279018773103</v>
+      </c>
+      <c r="H38">
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -1420,17 +1657,23 @@
       <c r="C39">
         <v>7.4349442379184977E-2</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="4">
+        <v>4.0627358605269901</v>
+      </c>
+      <c r="E39">
         <v>6.1919504643962855E-2</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>4.337050805452574E-2</v>
       </c>
-      <c r="F39">
+      <c r="G39" s="4">
+        <v>15.672388949821199</v>
+      </c>
+      <c r="H39">
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>41</v>
       </c>
@@ -1440,17 +1683,23 @@
       <c r="C40">
         <v>7.4390924307223244E-2</v>
       </c>
-      <c r="D40">
-        <v>0</v>
+      <c r="D40" s="4">
+        <v>-2.1764169840381098</v>
       </c>
       <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
         <v>6.199243692263906E-3</v>
       </c>
-      <c r="F40">
+      <c r="G40" s="4">
+        <v>-5.05765726168989</v>
+      </c>
+      <c r="H40">
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -1460,17 +1709,23 @@
       <c r="C41">
         <v>0.15441630636195181</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="4">
+        <v>-4.8039732434816003</v>
+      </c>
+      <c r="E41">
         <v>0.12330456226880394</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>6.7943174799253186E-2</v>
       </c>
-      <c r="F41">
+      <c r="G41" s="4">
+        <v>-1.6161573877381099</v>
+      </c>
+      <c r="H41">
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>43</v>
       </c>
@@ -1480,17 +1735,23 @@
       <c r="C42">
         <v>9.2838674763987078E-2</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="4">
+        <v>-4.6116622363838999</v>
+      </c>
+      <c r="E42">
         <v>6.0096153846153848E-2</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>4.8102940292222632E-2</v>
       </c>
-      <c r="F42">
+      <c r="G42" s="4">
+        <v>-6.8669082868646001</v>
+      </c>
+      <c r="H42">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -1500,17 +1761,23 @@
       <c r="C43">
         <v>9.8901098901096413E-2</v>
       </c>
-      <c r="D43">
-        <v>0</v>
+      <c r="D43" s="4">
+        <v>-1.4879117881834101</v>
       </c>
       <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
         <v>4.9450549450554451E-2</v>
       </c>
-      <c r="F43">
+      <c r="G43" s="4">
+        <v>13.759893603973</v>
+      </c>
+      <c r="H43">
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>45</v>
       </c>
@@ -1520,17 +1787,23 @@
       <c r="C44">
         <v>0.13044187184086586</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="4">
+        <v>13.206327823355</v>
+      </c>
+      <c r="E44">
         <v>5.428881650380022E-2</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>4.8915701940327787E-2</v>
       </c>
-      <c r="F44">
+      <c r="G44" s="4">
+        <v>-1.0670835137542001</v>
+      </c>
+      <c r="H44">
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>46</v>
       </c>
@@ -1540,17 +1813,23 @@
       <c r="C45">
         <v>3.7525463707518247E-2</v>
       </c>
-      <c r="D45">
-        <v>0</v>
+      <c r="D45" s="4">
+        <v>-5.0948550401602004</v>
       </c>
       <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
         <v>1.6082341588945098E-2</v>
       </c>
-      <c r="F45">
+      <c r="G45" s="4">
+        <v>-1.8330366653301899</v>
+      </c>
+      <c r="H45">
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -1560,17 +1839,23 @@
       <c r="C46">
         <v>6.3481986986195074E-2</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="4">
+        <v>-3.8863104580327099</v>
+      </c>
+      <c r="E46">
         <v>5.2854122621564484E-2</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>2.116066232872367E-2</v>
       </c>
-      <c r="F46">
+      <c r="G46" s="4">
+        <v>15.107644101561</v>
+      </c>
+      <c r="H46">
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -1580,17 +1865,23 @@
       <c r="C47">
         <v>8.3682008368196087E-2</v>
       </c>
-      <c r="D47">
-        <v>0</v>
+      <c r="D47" s="4">
+        <v>18.959722592064001</v>
       </c>
       <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
         <v>5.2301255230077955E-3</v>
       </c>
-      <c r="F47">
+      <c r="G47" s="4">
+        <v>13.67849971315</v>
+      </c>
+      <c r="H47">
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>49</v>
       </c>
@@ -1600,17 +1891,23 @@
       <c r="C48">
         <v>5.6462375526133687E-2</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="4">
+        <v>14.660295478435</v>
+      </c>
+      <c r="E48">
         <v>5.1308363263211899E-2</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>3.0797659377894283E-2</v>
       </c>
-      <c r="F48">
+      <c r="G48" s="4">
+        <v>4.1286113894249903</v>
+      </c>
+      <c r="H48">
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -1620,17 +1917,23 @@
       <c r="C49">
         <v>-1.0846575193872665E-2</v>
       </c>
-      <c r="D49">
-        <v>0</v>
+      <c r="D49" s="4">
+        <v>-10.080755552911199</v>
       </c>
       <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
         <v>-1.6269862790821328E-2</v>
       </c>
-      <c r="F49">
+      <c r="G49" s="4">
+        <v>12.119727950512001</v>
+      </c>
+      <c r="H49">
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -1640,17 +1943,23 @@
       <c r="C50">
         <v>8.6594144071014567E-2</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="4">
+        <v>-7.2788929117806997</v>
+      </c>
+      <c r="E50">
         <v>5.4054054054054057E-2</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>5.9533474048824829E-2</v>
       </c>
-      <c r="F50">
+      <c r="G50" s="4">
+        <v>-6.3862051630281096</v>
+      </c>
+      <c r="H50">
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -1660,17 +1969,23 @@
       <c r="C51">
         <v>6.9567078717822792E-2</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="4">
+        <v>-7.3153395010538</v>
+      </c>
+      <c r="E51">
         <v>0.10678056593699946</v>
       </c>
-      <c r="E51">
-        <v>0</v>
-      </c>
       <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51" s="4">
+        <v>-3.9535175836662999</v>
+      </c>
+      <c r="H51">
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -1680,17 +1995,23 @@
       <c r="C52">
         <v>1.0417751849153322E-2</v>
       </c>
-      <c r="D52">
-        <v>0</v>
+      <c r="D52" s="4">
+        <v>-7.9872818261303999</v>
       </c>
       <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
         <v>5.2088759245707394E-3</v>
       </c>
-      <c r="F52">
+      <c r="G52" s="4">
+        <v>-5.8898799499325998</v>
+      </c>
+      <c r="H52">
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>54</v>
       </c>
@@ -1700,17 +2021,23 @@
       <c r="C53">
         <v>0.1396990343610563</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="4">
+        <v>-5.5436429358396904</v>
+      </c>
+      <c r="E53">
         <v>0.14691478942213515</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <v>0.17156021763639037</v>
       </c>
-      <c r="F53">
+      <c r="G53" s="4">
+        <v>1.8169171207539501</v>
+      </c>
+      <c r="H53">
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>55</v>
       </c>
@@ -1720,17 +2047,23 @@
       <c r="C54">
         <v>0.10156212216471971</v>
       </c>
-      <c r="D54">
-        <v>0</v>
+      <c r="D54" s="4">
+        <v>-2.1995879097293001</v>
       </c>
       <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
         <v>6.7708081443131798E-2</v>
       </c>
-      <c r="F54">
+      <c r="G54" s="4">
+        <v>-5.8894040411267001</v>
+      </c>
+      <c r="H54">
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>56</v>
       </c>
@@ -1740,17 +2073,23 @@
       <c r="C55">
         <v>2.3828813801648949E-2</v>
       </c>
-      <c r="D55">
-        <v>0</v>
+      <c r="D55" s="4">
+        <v>-3.1837056331892</v>
       </c>
       <c r="E55">
         <v>0</v>
       </c>
       <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55" s="4">
+        <v>-6.6497630511838004</v>
+      </c>
+      <c r="H55">
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>57</v>
       </c>
@@ -1760,17 +2099,23 @@
       <c r="C56">
         <v>5.1626226122866152E-2</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="4">
+        <v>-2.4726769639827002</v>
+      </c>
+      <c r="E56">
         <v>4.6904315196998121E-2</v>
       </c>
-      <c r="E56">
+      <c r="F56">
         <v>1.8773173135572172E-2</v>
       </c>
-      <c r="F56">
+      <c r="G56" s="4">
+        <v>10.805350945416</v>
+      </c>
+      <c r="H56">
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -1780,17 +2125,23 @@
       <c r="C57">
         <v>0.11099292420108638</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="4">
+        <v>-6.5595408411823</v>
+      </c>
+      <c r="E57">
         <v>-4.6210720887245843E-2</v>
       </c>
-      <c r="E57">
+      <c r="F57">
         <v>-9.2494103500817687E-3</v>
       </c>
-      <c r="F57">
+      <c r="G57" s="4">
+        <v>-3.7345979315448998</v>
+      </c>
+      <c r="H57">
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>59</v>
       </c>
@@ -1800,17 +2151,23 @@
       <c r="C58">
         <v>4.5363817818907637E-2</v>
       </c>
-      <c r="D58">
-        <v>0</v>
+      <c r="D58" s="4">
+        <v>-1.6049312767193999</v>
       </c>
       <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
         <v>4.5363817818907637E-2</v>
       </c>
-      <c r="F58">
+      <c r="G58" s="4">
+        <v>13.676091694169999</v>
+      </c>
+      <c r="H58">
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>60</v>
       </c>
@@ -1820,17 +2177,23 @@
       <c r="C59">
         <v>6.3002810894648723E-2</v>
       </c>
-      <c r="D59">
-        <v>0</v>
+      <c r="D59" s="4">
+        <v>-2.3190160408804901</v>
       </c>
       <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
         <v>1.9385480275278227E-2</v>
       </c>
-      <c r="F59">
+      <c r="G59" s="4">
+        <v>-6.8458411651251998</v>
+      </c>
+      <c r="H59">
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>61</v>
       </c>
@@ -1840,17 +2203,23 @@
       <c r="C60">
         <v>3.4321297547778788E-2</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="4">
+        <v>12.815512057559999</v>
+      </c>
+      <c r="E60">
         <v>0.1445086705202312</v>
       </c>
-      <c r="E60">
-        <v>0</v>
-      </c>
       <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60" s="4">
+        <v>18.230440572702999</v>
+      </c>
+      <c r="H60">
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>62</v>
       </c>
@@ -1860,17 +2229,23 @@
       <c r="C61">
         <v>0.12774413323239112</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="4">
+        <v>-2.1497852375706898</v>
+      </c>
+      <c r="E61">
         <v>0.14164305949008499</v>
       </c>
-      <c r="E61">
+      <c r="F61">
         <v>4.258137774413754E-2</v>
       </c>
-      <c r="F61">
+      <c r="G61" s="4">
+        <v>-0.42321095690980498</v>
+      </c>
+      <c r="H61">
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>63</v>
       </c>
@@ -1880,17 +2255,23 @@
       <c r="C62">
         <v>9.6587250482932083E-2</v>
       </c>
-      <c r="D62">
-        <v>0</v>
+      <c r="D62" s="4">
+        <v>-5.0342693336049003</v>
       </c>
       <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
         <v>4.5993928801398222E-2</v>
       </c>
-      <c r="F62">
+      <c r="G62" s="4">
+        <v>-1.9931522545114</v>
+      </c>
+      <c r="H62">
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>64</v>
       </c>
@@ -1900,17 +2281,23 @@
       <c r="C63">
         <v>0</v>
       </c>
-      <c r="D63">
-        <v>0</v>
+      <c r="D63" s="4">
+        <v>-3.7938654621729899</v>
       </c>
       <c r="E63">
         <v>0</v>
       </c>
       <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63" s="4">
+        <v>-1.558961544095</v>
+      </c>
+      <c r="H63">
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>65</v>
       </c>
@@ -1920,17 +2307,23 @@
       <c r="C64">
         <v>2.6779907418044792E-2</v>
       </c>
-      <c r="D64">
-        <v>0</v>
+      <c r="D64" s="4">
+        <v>12.452210620158001</v>
       </c>
       <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
         <v>3.8257010597157141E-3</v>
       </c>
-      <c r="F64">
+      <c r="G64" s="4">
+        <v>-2.9740069173000001</v>
+      </c>
+      <c r="H64">
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>66</v>
       </c>
@@ -1940,17 +2333,23 @@
       <c r="C65">
         <v>7.9365079365007179E-3</v>
       </c>
-      <c r="D65">
-        <v>0</v>
+      <c r="D65" s="4">
+        <v>9.8450215887730206</v>
       </c>
       <c r="E65">
         <v>0</v>
       </c>
       <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65" s="4">
+        <v>5.8880256260951302</v>
+      </c>
+      <c r="H65">
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>67</v>
       </c>
@@ -1960,17 +2359,23 @@
       <c r="C66">
         <v>-7.6813765026797582E-3</v>
       </c>
-      <c r="D66">
-        <v>0</v>
+      <c r="D66" s="4">
+        <v>13.4811491761665</v>
       </c>
       <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
         <v>-1.1522064754010904E-2</v>
       </c>
-      <c r="F66">
+      <c r="G66" s="4">
+        <v>-2.0678442598090099</v>
+      </c>
+      <c r="H66">
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>68</v>
       </c>
@@ -1980,17 +2385,23 @@
       <c r="C67">
         <v>3.7091988130530064E-3</v>
       </c>
-      <c r="D67">
-        <v>0</v>
+      <c r="D67" s="4">
+        <v>16.843077678949999</v>
       </c>
       <c r="E67">
         <v>0</v>
       </c>
       <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67" s="4">
+        <v>-1.5097015611011999</v>
+      </c>
+      <c r="H67">
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>69</v>
       </c>
@@ -2000,17 +2411,23 @@
       <c r="C68">
         <v>0</v>
       </c>
-      <c r="D68">
-        <v>0</v>
+      <c r="D68" s="4">
+        <v>-3.7157201751022</v>
       </c>
       <c r="E68">
         <v>0</v>
       </c>
       <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68" s="4">
+        <v>10.4912489065416</v>
+      </c>
+      <c r="H68">
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>70</v>
       </c>
@@ -2020,17 +2437,23 @@
       <c r="C69">
         <v>0</v>
       </c>
-      <c r="D69">
-        <v>0</v>
+      <c r="D69" s="4">
+        <v>-6.6322951796348004</v>
       </c>
       <c r="E69">
         <v>0</v>
       </c>
       <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69" s="4">
+        <v>15.6816599295381</v>
+      </c>
+      <c r="H69">
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -2040,17 +2463,23 @@
       <c r="C70">
         <v>0</v>
       </c>
-      <c r="D70">
-        <v>0</v>
+      <c r="D70" s="4">
+        <v>11.596440486193</v>
       </c>
       <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
         <v>3.8124285169618397E-3</v>
       </c>
-      <c r="F70">
+      <c r="G70" s="4">
+        <v>14.92135103747</v>
+      </c>
+      <c r="H70">
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>72</v>
       </c>
@@ -2060,17 +2489,23 @@
       <c r="C71">
         <v>0.10181491464510634</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="4">
+        <v>1.3708510344553999</v>
+      </c>
+      <c r="E71">
         <v>3.5906642728904849E-2</v>
       </c>
-      <c r="E71">
+      <c r="F71">
         <v>1.4375561545376135E-2</v>
       </c>
-      <c r="F71">
+      <c r="G71" s="4">
+        <v>-3.3558572971484</v>
+      </c>
+      <c r="H71">
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>73</v>
       </c>
@@ -2080,17 +2515,23 @@
       <c r="C72">
         <v>8.1007189388045908E-2</v>
       </c>
-      <c r="D72">
-        <v>0</v>
+      <c r="D72" s="4">
+        <v>-1.78036790107499</v>
       </c>
       <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
         <v>6.7505991156653769E-3</v>
       </c>
-      <c r="F72">
+      <c r="G72" s="4">
+        <v>-4.0305773311130002</v>
+      </c>
+      <c r="H72">
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>74</v>
       </c>
@@ -2100,17 +2541,23 @@
       <c r="C73">
         <v>0</v>
       </c>
-      <c r="D73">
-        <v>0</v>
+      <c r="D73" s="4">
+        <v>-3.738308607659</v>
       </c>
       <c r="E73">
         <v>0</v>
       </c>
       <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73" s="4">
+        <v>-3.4920206140499901</v>
+      </c>
+      <c r="H73">
         <v>71</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>75</v>
       </c>
@@ -2120,17 +2567,23 @@
       <c r="C74">
         <v>6.7453625632316388E-3</v>
       </c>
-      <c r="D74">
-        <v>0</v>
+      <c r="D74" s="4">
+        <v>10.38831732695</v>
       </c>
       <c r="E74">
         <v>0</v>
       </c>
       <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74" s="4">
+        <v>-6.2303974405620002</v>
+      </c>
+      <c r="H74">
         <v>72</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>76</v>
       </c>
@@ -2140,17 +2593,23 @@
       <c r="C75">
         <v>0</v>
       </c>
-      <c r="D75">
-        <v>0</v>
+      <c r="D75" s="4">
+        <v>-4.8329744372199999</v>
       </c>
       <c r="E75">
         <v>0</v>
       </c>
       <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75" s="4">
+        <v>-4.1107631234591997</v>
+      </c>
+      <c r="H75">
         <v>73</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>77</v>
       </c>
@@ -2160,17 +2619,23 @@
       <c r="C76">
         <v>0</v>
       </c>
-      <c r="D76">
-        <v>0</v>
+      <c r="D76" s="4">
+        <v>-3.5322457107403902</v>
       </c>
       <c r="E76">
         <v>0</v>
       </c>
       <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76" s="4">
+        <v>3.2800818263990101</v>
+      </c>
+      <c r="H76">
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>78</v>
       </c>
@@ -2180,17 +2645,23 @@
       <c r="C77">
         <v>1.3008553123681777E-2</v>
       </c>
-      <c r="D77">
-        <v>0</v>
+      <c r="D77" s="4">
+        <v>16.327649439384999</v>
       </c>
       <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
         <v>1.3008553123681777E-2</v>
       </c>
-      <c r="F77">
+      <c r="G77" s="4">
+        <v>-1.56888002295999</v>
+      </c>
+      <c r="H77">
         <v>75</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>79</v>
       </c>
@@ -2200,17 +2671,23 @@
       <c r="C78">
         <v>0</v>
       </c>
-      <c r="D78">
-        <v>0</v>
+      <c r="D78" s="4">
+        <v>-1.4147468130067899</v>
       </c>
       <c r="E78">
         <v>0</v>
       </c>
       <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78" s="4">
+        <v>-6.4690940990199897</v>
+      </c>
+      <c r="H78">
         <v>76</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>80</v>
       </c>
@@ -2220,17 +2697,23 @@
       <c r="C79">
         <v>4.6199225274536473E-2</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="4">
+        <v>-5.3924178982600104</v>
+      </c>
+      <c r="E79">
         <v>3.5536602700781808E-2</v>
       </c>
-      <c r="E79">
+      <c r="F79">
         <v>3.1984079036216313E-2</v>
       </c>
-      <c r="F79">
+      <c r="G79" s="4">
+        <v>12.084818677446</v>
+      </c>
+      <c r="H79">
         <v>77</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>81</v>
       </c>
@@ -2240,17 +2723,23 @@
       <c r="C80">
         <v>3.3636057854019512E-2</v>
       </c>
-      <c r="D80">
-        <v>0</v>
+      <c r="D80" s="4">
+        <v>-4.9249539840610996</v>
       </c>
       <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
         <v>2.354524049780754E-2</v>
       </c>
-      <c r="F80">
+      <c r="G80" s="4">
+        <v>13.547065147411001</v>
+      </c>
+      <c r="H80">
         <v>78</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>82</v>
       </c>
@@ -2260,17 +2749,23 @@
       <c r="C81">
         <v>5.057049843547233E-2</v>
       </c>
-      <c r="D81">
-        <v>0</v>
+      <c r="D81" s="4">
+        <v>-3.6185784589786101</v>
       </c>
       <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
         <v>2.528524921774335E-2</v>
       </c>
-      <c r="F81">
+      <c r="G81" s="4">
+        <v>-2.1444393615192001</v>
+      </c>
+      <c r="H81">
         <v>79</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -2280,17 +2775,23 @@
       <c r="C82">
         <v>2.6583961010193207E-2</v>
       </c>
-      <c r="D82">
-        <v>0</v>
+      <c r="D82" s="4">
+        <v>-7.1516647113621996</v>
       </c>
       <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
         <v>2.6583961010193207E-2</v>
       </c>
-      <c r="F82">
+      <c r="G82" s="4">
+        <v>-2.1754591338109002</v>
+      </c>
+      <c r="H82">
         <v>80</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>84</v>
       </c>
@@ -2300,17 +2801,23 @@
       <c r="C83">
         <v>0</v>
       </c>
-      <c r="D83">
-        <v>0</v>
+      <c r="D83" s="4">
+        <v>5.2040696321220103</v>
       </c>
       <c r="E83">
         <v>0</v>
       </c>
       <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83" s="4">
+        <v>-1.4826015083132</v>
+      </c>
+      <c r="H83">
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>85</v>
       </c>
@@ -2320,17 +2827,23 @@
       <c r="C84">
         <v>0</v>
       </c>
-      <c r="D84">
-        <v>0</v>
+      <c r="D84" s="4">
+        <v>2.1811751714909899</v>
       </c>
       <c r="E84">
         <v>0</v>
       </c>
       <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84" s="4">
+        <v>5.1192193711139904</v>
+      </c>
+      <c r="H84">
         <v>82</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>86</v>
       </c>
@@ -2340,17 +2853,23 @@
       <c r="C85">
         <v>0</v>
       </c>
-      <c r="D85">
-        <v>0</v>
+      <c r="D85" s="4">
+        <v>-3.5383180540700998</v>
       </c>
       <c r="E85">
         <v>0</v>
       </c>
       <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85" s="4">
+        <v>-1.7679379683512999</v>
+      </c>
+      <c r="H85">
         <v>83</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>87</v>
       </c>
@@ -2360,17 +2879,23 @@
       <c r="C86">
         <v>0</v>
       </c>
-      <c r="D86">
-        <v>0</v>
+      <c r="D86" s="4">
+        <v>-2.5120409536799899</v>
       </c>
       <c r="E86">
         <v>0</v>
       </c>
       <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86" s="4">
+        <v>-2.6569248163222099</v>
+      </c>
+      <c r="H86">
         <v>84</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>88</v>
       </c>
@@ -2380,17 +2905,23 @@
       <c r="C87">
         <v>2.912310335786733E-3</v>
       </c>
-      <c r="D87">
-        <v>0</v>
+      <c r="D87" s="4">
+        <v>-2.52779238071331</v>
       </c>
       <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
         <v>8.7369310073601991E-3</v>
       </c>
-      <c r="F87">
+      <c r="G87" s="4">
+        <v>-2.89311531143899</v>
+      </c>
+      <c r="H87">
         <v>85</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>89</v>
       </c>
@@ -2400,17 +2931,23 @@
       <c r="C88">
         <v>-8.0040553880681396E-3</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="4">
+        <v>2.503402092115</v>
+      </c>
+      <c r="E88">
         <v>2.6666666666666668E-2</v>
       </c>
-      <c r="E88">
+      <c r="F88">
         <v>1.8676129238809479E-2</v>
       </c>
-      <c r="F88">
+      <c r="G88" s="4">
+        <v>9.0196529545872899</v>
+      </c>
+      <c r="H88">
         <v>86</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>90</v>
       </c>
@@ -2420,17 +2957,23 @@
       <c r="C89">
         <v>2.5657472738941051E-2</v>
       </c>
-      <c r="D89">
-        <v>0</v>
+      <c r="D89" s="4">
+        <v>12.920804886921999</v>
       </c>
       <c r="E89">
         <v>0</v>
       </c>
       <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89" s="4">
+        <v>13.880586402613</v>
+      </c>
+      <c r="H89">
         <v>87</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>91</v>
       </c>
@@ -2440,17 +2983,23 @@
       <c r="C90">
         <v>2.7238885021642536E-2</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="4">
+        <v>-3.0542340989658001</v>
+      </c>
+      <c r="E90">
         <v>3.02571860816944E-2</v>
       </c>
-      <c r="E90">
+      <c r="F90">
         <v>1.2106171120731545E-2</v>
       </c>
-      <c r="F90">
+      <c r="G90" s="4">
+        <v>-3.9744415919309901</v>
+      </c>
+      <c r="H90">
         <v>88</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>92</v>
       </c>
@@ -2460,17 +3009,23 @@
       <c r="C91">
         <v>6.515580736544424E-2</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="4">
+        <v>12.729093969148</v>
+      </c>
+      <c r="E91">
         <v>2.8312570781426957E-2</v>
       </c>
-      <c r="E91">
+      <c r="F91">
         <v>1.4164305949008497E-2</v>
       </c>
-      <c r="F91">
+      <c r="G91" s="4">
+        <v>13.802837840397199</v>
+      </c>
+      <c r="H91">
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>93</v>
       </c>
@@ -2480,13 +3035,19 @@
       <c r="C92">
         <v>3.6990065525261337E-2</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="4">
+        <v>-4.9870352474502999</v>
+      </c>
+      <c r="E92">
         <v>2.6413100898045432E-2</v>
       </c>
-      <c r="E92">
+      <c r="F92">
         <v>2.1137180300152766E-2</v>
       </c>
-      <c r="F92">
+      <c r="G92" s="4">
+        <v>-3.3223513446467998</v>
+      </c>
+      <c r="H92">
         <v>90</v>
       </c>
     </row>
@@ -2494,7 +3055,7 @@
   <mergeCells count="3">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="E1:F1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
